--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513654_FASEFINALAFFA2_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513654_FASEFINALAFFA2_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7761</v>
+        <v>4.8434</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4982</v>
+        <v>4.3985</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2779</v>
+        <v>0.4448</v>
       </c>
       <c r="G2" t="n">
         <v>1.4072</v>
@@ -610,13 +610,13 @@
         <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8005</v>
+        <v>-0.7333</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0462</v>
+        <v>-0.0535</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8467</v>
+        <v>-0.6797</v>
       </c>
       <c r="V2" t="n">
         <v>3.0011</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4827</v>
+        <v>4.2625</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6995</v>
+        <v>1.2011</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7832</v>
+        <v>3.0614</v>
       </c>
       <c r="G3" t="n">
         <v>2.8984</v>
@@ -688,13 +688,13 @@
         <v>1.7526</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0526</v>
+        <v>-0.2727</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6488</v>
+        <v>0.1504</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7014</v>
+        <v>-0.4232</v>
       </c>
       <c r="V3" t="n">
         <v>1.8316</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8775</v>
+        <v>2.9099</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8194</v>
+        <v>2.0188</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0581</v>
+        <v>0.8911</v>
       </c>
       <c r="G4" t="n">
         <v>2.8</v>
@@ -766,13 +766,13 @@
         <v>1.1684</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1667</v>
+        <v>-0.1343</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2012</v>
+        <v>-0.0018</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0345</v>
+        <v>-0.1325</v>
       </c>
       <c r="V4" t="n">
         <v>0.2442</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6279</v>
+        <v>2.1936</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2158</v>
+        <v>2.6145</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5879</v>
+        <v>-0.4209</v>
       </c>
       <c r="G5" t="n">
         <v>2.2245</v>
@@ -844,13 +844,13 @@
         <v>1.5579</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1808</v>
+        <v>-0.6151</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4947</v>
+        <v>-0.096</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6861</v>
+        <v>-0.5192</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1257</v>
+        <v>1.8513</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0238</v>
+        <v>-0.3261</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1496</v>
+        <v>2.1774</v>
       </c>
       <c r="G6" t="n">
         <v>2.6836</v>
@@ -922,13 +922,13 @@
         <v>1.7526</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0816</v>
+        <v>-0.356</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.1061</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2777</v>
+        <v>-0.2499</v>
       </c>
       <c r="V6" t="n">
         <v>-0.0868</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7116</v>
+        <v>0.3692</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5547</v>
+        <v>1.0208</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2662</v>
+        <v>-0.6516</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2215</v>
+        <v>-0.0595</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4045</v>
+        <v>0.1545</v>
       </c>
       <c r="I7" t="n">
-        <v>0.183</v>
+        <v>-0.214</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.4085</v>
+        <v>0.6654</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2822</v>
+        <v>1.265</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.1264</v>
+        <v>-0.5995</v>
       </c>
       <c r="M7" t="n">
-        <v>0.187</v>
+        <v>-0.7249</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1223</v>
+        <v>-1.1105</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3093</v>
+        <v>0.3856</v>
       </c>
       <c r="P7" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9737</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-3.1158</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.1421</v>
+        <v>1.3632</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4931</v>
+        <v>-0.2566</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1897</v>
+        <v>0.108</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3034</v>
+        <v>-0.3646</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4137</v>
+        <v>0.2958</v>
       </c>
       <c r="W7" t="n">
-        <v>1.78</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3663</v>
+        <v>-0.9253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1466</v>
+        <v>-0.5194</v>
       </c>
       <c r="E8" t="n">
-        <v>1.0208</v>
+        <v>-2.4517</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8742</v>
+        <v>1.9323</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0595</v>
+        <v>-1.2215</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1545</v>
+        <v>-1.4045</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.214</v>
+        <v>0.183</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6654</v>
+        <v>-1.4085</v>
       </c>
       <c r="K8" t="n">
-        <v>1.265</v>
+        <v>-0.2822</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5995</v>
+        <v>-1.1264</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7249</v>
+        <v>0.187</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1105</v>
+        <v>-1.1223</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3856</v>
+        <v>1.3093</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3895</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9737</v>
+        <v>-3.1158</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3632</v>
+        <v>2.1421</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4792</v>
+        <v>0.2621</v>
       </c>
       <c r="T8" t="n">
-        <v>0.108</v>
+        <v>0.2926</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.0305</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2958</v>
+        <v>1.4137</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2211</v>
+        <v>1.78</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9253</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0173</v>
+        <v>-2.1338</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0986</v>
+        <v>-2.361</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0813</v>
+        <v>0.2273</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2273</v>
+        <v>-2.5538</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7976</v>
+        <v>-2.8977</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5703</v>
+        <v>0.3439</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6077</v>
+        <v>-1.4289</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2674</v>
+        <v>-1.9319</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3403</v>
+        <v>0.503</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3804</v>
+        <v>-1.1249</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5302</v>
+        <v>-0.9658</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9106</v>
+        <v>-0.1591</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1947</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1421</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9474</v>
+        <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5674</v>
+        <v>-0.5115</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3133</v>
+        <v>0.0415</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2541</v>
+        <v>-0.5531</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1626</v>
+        <v>0.3474</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5005</v>
+        <v>0.3474</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8153</v>
+        <v>-3.3874</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9591</v>
+        <v>-3.9957</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1438</v>
+        <v>0.6083</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5538</v>
+        <v>-1.2273</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8977</v>
+        <v>-1.7976</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3439</v>
+        <v>0.5703</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4289</v>
+        <v>-1.6077</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9319</v>
+        <v>-1.2674</v>
       </c>
       <c r="L10" t="n">
-        <v>0.503</v>
+        <v>-0.3403</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1249</v>
+        <v>0.3804</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9658</v>
+        <v>-0.5302</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1591</v>
+        <v>0.9106</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5842000000000001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9737</v>
+        <v>-2.1421</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5579</v>
+        <v>1.9474</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1931</v>
+        <v>0.1973</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>0.4163</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6365</v>
+        <v>-0.219</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3474</v>
+        <v>-2.1626</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3474</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0263</v>
+        <v>-3.5</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7014</v>
+        <v>-4.203</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6751</v>
+        <v>0.703</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0961</v>
@@ -1312,13 +1312,13 @@
         <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5934</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4328</v>
+        <v>0.0655</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1605</v>
+        <v>-0.1327</v>
       </c>
       <c r="V11" t="n">
         <v>0.6105</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.8892</v>
+        <v>6.8893</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0839</v>
+        <v>-2.0838</v>
       </c>
       <c r="F12" t="n">
-        <v>8.973100000000001</v>
+        <v>8.973099999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8555</v>
+        <v>4.855500000000001</v>
       </c>
       <c r="H12" t="n">
         <v>-10.625</v>
@@ -1372,7 +1372,7 @@
         <v>8.334800000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03159999999999991</v>
+        <v>-0.03159999999999985</v>
       </c>
       <c r="N12" t="n">
         <v>-7.177099999999999</v>
@@ -1381,7 +1381,7 @@
         <v>7.1457</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9736999999999998</v>
+        <v>-0.9736999999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-17.5264</v>
@@ -1390,13 +1390,13 @@
         <v>16.5526</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4874</v>
+        <v>-2.4872</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8169000000000002</v>
+        <v>0.8169000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.3041</v>
+        <v>-3.3044</v>
       </c>
       <c r="V12" t="n">
         <v>5.494900000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. CRESPO MONTESINOS</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3943</v>
+        <v>3.6256</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8064</v>
+        <v>3.498</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4121</v>
+        <v>0.1275</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4751</v>
+        <v>1.8825</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3017</v>
+        <v>3.1764</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1734</v>
+        <v>-1.2939</v>
       </c>
       <c r="J13" t="n">
-        <v>1.534</v>
+        <v>2.7495</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.3385</v>
+        <v>2.6684</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8726</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0091</v>
+        <v>-0.867</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0369</v>
+        <v>0.508</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.046</v>
+        <v>-1.3749</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7789</v>
+        <v>1.9474</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9737</v>
+        <v>-0.1947</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7526</v>
+        <v>2.1421</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5899</v>
+        <v>-0.2559</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4661</v>
+        <v>-0.2778</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1238</v>
+        <v>0.0219</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5005</v>
+        <v>0.0516</v>
       </c>
       <c r="W13" t="n">
-        <v>1.78</v>
+        <v>1.2211</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2795</v>
+        <v>-1.1695</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>C. CRESPO MONTESINOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7763</v>
+        <v>3.0545</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3983</v>
+        <v>3.411</v>
       </c>
       <c r="F14" t="n">
-        <v>0.378</v>
+        <v>-0.3565</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8825</v>
+        <v>-0.4751</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1764</v>
+        <v>-0.3017</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.2939</v>
+        <v>-0.1734</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7495</v>
+        <v>1.534</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6684</v>
+        <v>-0.3385</v>
       </c>
       <c r="L14" t="n">
-        <v>0.08110000000000001</v>
+        <v>1.8726</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.867</v>
+        <v>-2.0091</v>
       </c>
       <c r="N14" t="n">
-        <v>0.508</v>
+        <v>0.0369</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3749</v>
+        <v>-2.046</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9474</v>
+        <v>0.7789</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1947</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1421</v>
+        <v>1.7526</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1051</v>
+        <v>1.2501</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3775</v>
+        <v>1.0706</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2723</v>
+        <v>0.1795</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0516</v>
+        <v>1.5005</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2211</v>
+        <v>1.78</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1695</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. MENDEZ BLANCO</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4358</v>
+        <v>0.1202</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0228</v>
+        <v>0.1202</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4586</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9852</v>
+        <v>0.0205</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5592</v>
+        <v>0.0205</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.574</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0465</v>
+        <v>0.0205</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9065</v>
+        <v>0.0205</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.953</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0317</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6526999999999999</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.379</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3895</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5579</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2237</v>
+        <v>0.0997</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8542</v>
+        <v>0.0997</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6304999999999999</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1626</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.5005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>C. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,49 +1657,49 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0205</v>
+        <v>-0.0105</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0205</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.0105</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0205</v>
+        <v>-0.2053</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0205</v>
+        <v>-0.2053</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0205</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0205</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. VILA DE MIGUEL</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0105</v>
+        <v>-0.1111</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1.3655</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0105</v>
+        <v>-1.4765</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2053</v>
+        <v>-0.1049</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2053</v>
+        <v>1.4142</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-1.5192</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.2423</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.7852</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.5429</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2053</v>
+        <v>-0.3472</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2053</v>
+        <v>0.629</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.9762</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1947</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1947</v>
+        <v>1.5579</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.6823</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.6479</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.0344</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.2726</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.449</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3026</v>
+        <v>-0.1913</v>
       </c>
       <c r="E18" t="n">
         <v>-0.7179</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4153</v>
+        <v>0.5266</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2521</v>
@@ -1858,13 +1858,13 @@
         <v>0.9737</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0927</v>
+        <v>0.204</v>
       </c>
       <c r="T18" t="n">
         <v>0.4172</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3245</v>
+        <v>-0.2132</v>
       </c>
       <c r="V18" t="n">
         <v>0.0516</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3266</v>
+        <v>-0.5337</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0664</v>
+        <v>-1.0337</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3931</v>
+        <v>0.4999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1049</v>
+        <v>0.7176</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4142</v>
+        <v>2.0192</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5192</v>
+        <v>-1.3016</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2423</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7852</v>
+        <v>1.9705</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5429</v>
+        <v>-1.2885</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3472</v>
+        <v>0.0356</v>
       </c>
       <c r="N19" t="n">
-        <v>0.629</v>
+        <v>0.0487</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9762</v>
+        <v>-0.0131</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5842000000000001</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5579</v>
+        <v>1.1684</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4667</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3489</v>
+        <v>0.2317</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1178</v>
+        <v>-0.1451</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2726</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>1.449</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.7216</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>O. MENDEZ BLANCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3946</v>
+        <v>-0.6096</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0337</v>
+        <v>-1.3186</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6391</v>
+        <v>0.709</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7176</v>
+        <v>0.9852</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0192</v>
+        <v>2.5592</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3016</v>
+        <v>-1.574</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6820000000000001</v>
+        <v>-0.0465</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9705</v>
+        <v>1.9065</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2885</v>
+        <v>-1.953</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0356</v>
+        <v>1.0317</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0487</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0131</v>
+        <v>0.379</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7789</v>
+        <v>0.3895</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9474</v>
+        <v>-1.1684</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1684</v>
+        <v>1.5579</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2257</v>
+        <v>0.1784</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2317</v>
+        <v>0.5584</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.006</v>
+        <v>-0.38</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-2.1626</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4462</v>
+        <v>-0.9083</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1045</v>
+        <v>1.5032</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5506</v>
+        <v>-2.4115</v>
       </c>
       <c r="G21" t="n">
         <v>0.6408</v>
@@ -2092,13 +2092,13 @@
         <v>1.7526</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3401</v>
+        <v>0.1977</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0775</v>
+        <v>0.3212</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2626</v>
+        <v>-0.1235</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5521</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7279</v>
+        <v>-1.5434</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1031</v>
+        <v>-2.8073</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3752</v>
+        <v>1.2639</v>
       </c>
       <c r="G22" t="n">
         <v>0.6719000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>1.5579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4203</v>
+        <v>0.7642</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9183</v>
+        <v>0.3775</v>
       </c>
       <c r="U22" t="n">
-        <v>0.498</v>
+        <v>0.3867</v>
       </c>
       <c r="V22" t="n">
         <v>0.3311</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8409</v>
+        <v>-3.3031</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1535</v>
+        <v>-2.7548</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6875</v>
+        <v>-0.5483</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6314</v>
@@ -2248,13 +2248,13 @@
         <v>1.9474</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3848</v>
+        <v>-0.847</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6802</v>
+        <v>-0.2815</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7047</v>
+        <v>-0.5655</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6037</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5997</v>
+        <v>-6.6113</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.2765</v>
+        <v>-10.1768</v>
       </c>
       <c r="F24" t="n">
-        <v>3.6768</v>
+        <v>3.5655</v>
       </c>
       <c r="G24" t="n">
         <v>-7.2381</v>
@@ -2326,13 +2326,13 @@
         <v>2.7263</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3337</v>
+        <v>0.3221</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1015</v>
+        <v>0.2012</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2322</v>
+        <v>0.1209</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2795</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.0221</v>
+        <v>-7.022</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.911400000000002</v>
+        <v>-8.911199999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>1.8892</v>
+        <v>1.8891</v>
       </c>
       <c r="G25" t="n">
         <v>-4.9884</v>
@@ -2380,7 +2380,7 @@
         <v>0.03159999999999918</v>
       </c>
       <c r="K25" t="n">
-        <v>7.177099999999999</v>
+        <v>7.177100000000001</v>
       </c>
       <c r="L25" t="n">
         <v>-7.1454</v>
@@ -2395,7 +2395,7 @@
         <v>-8.467799999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7789999999999998</v>
+        <v>0.7790000000000002</v>
       </c>
       <c r="Q25" t="n">
         <v>-16.5526</v>
@@ -2410,7 +2410,7 @@
         <v>3.3661</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6842</v>
+        <v>-0.6839</v>
       </c>
       <c r="V25" t="n">
         <v>-5.494699999999999</v>
